--- a/data/trans_orig/dukeCONF-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo confidencial (Duke)</t>
+          <t>Puntuación media de la escala de apoyo confidencial (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 30,06</t>
+          <t>29,33; 30,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 31,5</t>
+          <t>30,76; 31,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 29,94</t>
+          <t>29,18; 29,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,15; 31,03</t>
+          <t>30,14; 31,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,08; 28,97</t>
+          <t>28,04; 28,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,01; 30,77</t>
+          <t>30,06; 30,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,74; 29,5</t>
+          <t>28,74; 29,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,93; 30,63</t>
+          <t>29,95; 30,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,83; 29,41</t>
+          <t>28,84; 29,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 31,08</t>
+          <t>30,55; 31,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,08; 29,64</t>
+          <t>29,07; 29,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 30,71</t>
+          <t>30,17; 30,72</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 30,45</t>
+          <t>29,75; 30,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,23; 30,87</t>
+          <t>30,21; 30,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 30,37</t>
+          <t>29,72; 30,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 33,07</t>
+          <t>30,47; 33,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,2; 29,92</t>
+          <t>29,18; 29,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,8; 30,43</t>
+          <t>29,82; 30,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 30,11</t>
+          <t>29,55; 30,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 30,35</t>
+          <t>29,72; 30,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 30,05</t>
+          <t>29,58; 30,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,12; 30,56</t>
+          <t>30,13; 30,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 30,13</t>
+          <t>29,71; 30,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,23; 32,15</t>
+          <t>30,21; 32,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,16; 30,98</t>
+          <t>30,11; 30,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 30,98</t>
+          <t>30,13; 30,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,74; 29,39</t>
+          <t>28,73; 29,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,25; 31,04</t>
+          <t>30,24; 31,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,41; 30,26</t>
+          <t>29,42; 30,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,63; 30,4</t>
+          <t>29,64; 30,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,63; 29,25</t>
+          <t>28,58; 29,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,17; 31,24</t>
+          <t>30,15; 31,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,88; 30,47</t>
+          <t>29,93; 30,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,03; 30,58</t>
+          <t>30,04; 30,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,76; 29,21</t>
+          <t>28,76; 29,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,34; 31,01</t>
+          <t>30,32; 30,98</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 30,21</t>
+          <t>29,55; 30,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,86; 30,52</t>
+          <t>29,9; 30,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 30,13</t>
+          <t>29,53; 30,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,36; 31,1</t>
+          <t>30,33; 31,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 29,71</t>
+          <t>28,95; 29,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 29,94</t>
+          <t>29,29; 29,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 29,99</t>
+          <t>29,33; 29,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 31,73</t>
+          <t>30,38; 31,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,36; 29,87</t>
+          <t>29,37; 29,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 30,12</t>
+          <t>29,67; 30,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 29,95</t>
+          <t>29,51; 29,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,26</t>
+          <t>30,48; 31,25</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,23</t>
+          <t>29,87; 30,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,39; 30,76</t>
+          <t>30,41; 30,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,82</t>
+          <t>29,51; 29,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,57; 31,96</t>
+          <t>30,57; 31,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,14; 29,52</t>
+          <t>29,16; 29,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,85; 30,19</t>
+          <t>29,86; 30,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 29,61</t>
+          <t>29,29; 29,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,23; 30,78</t>
+          <t>30,24; 30,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,57; 29,83</t>
+          <t>29,56; 29,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,67</t>
+          <t>29,44; 29,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,27</t>
+          <t>30,47; 31,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeCONF-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeCONF-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30,24</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,44</t>
+          <t>30,32</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 30,11</t>
+          <t>29,33; 30,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 31,48</t>
+          <t>30,79; 31,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 29,96</t>
+          <t>29,15; 29,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,14; 31,07</t>
+          <t>29,91; 30,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,04; 28,96</t>
+          <t>28,11; 28,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,06; 30,79</t>
+          <t>30,04; 30,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,74; 29,53</t>
+          <t>28,75; 29,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,95; 30,6</t>
+          <t>29,89; 30,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 29,41</t>
+          <t>28,83; 29,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 31,05</t>
+          <t>30,54; 31,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 29,62</t>
+          <t>29,07; 29,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,17; 30,72</t>
+          <t>30,02; 30,59</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,48</t>
+          <t>30,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,05</t>
+          <t>29,94</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,84</t>
+          <t>30,2</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 30,45</t>
+          <t>29,73; 30,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 30,82</t>
+          <t>30,22; 30,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 30,33</t>
+          <t>29,74; 30,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 33,18</t>
+          <t>30,06; 30,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,18; 29,86</t>
+          <t>29,18; 29,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 30,49</t>
+          <t>29,82; 30,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 30,08</t>
+          <t>29,53; 30,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 30,35</t>
+          <t>29,6; 30,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 30,07</t>
+          <t>29,59; 30,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,13; 30,56</t>
+          <t>30,1; 30,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,71; 30,15</t>
+          <t>29,72; 30,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 32,24</t>
+          <t>29,96; 30,43</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,65</t>
+          <t>30,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,56</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,36</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,11; 30,95</t>
+          <t>30,15; 30,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,13; 30,96</t>
+          <t>30,19; 30,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,73; 29,36</t>
+          <t>28,75; 29,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 31,02</t>
+          <t>30,06; 30,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,42; 30,31</t>
+          <t>29,4; 30,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,58; 29,24</t>
+          <t>28,6; 29,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,15; 31,19</t>
+          <t>29,96; 30,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,93; 30,49</t>
+          <t>29,85; 30,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,04; 30,6</t>
+          <t>30,01; 30,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,76; 29,22</t>
+          <t>28,75; 29,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 30,98</t>
+          <t>30,1; 30,62</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,78</t>
+          <t>30,34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,74</t>
+          <t>30,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 30,25</t>
+          <t>29,55; 30,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 30,53</t>
+          <t>29,86; 30,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,53; 30,12</t>
+          <t>29,53; 30,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 31,04</t>
+          <t>30,15; 30,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 29,69</t>
+          <t>28,98; 29,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,29; 29,94</t>
+          <t>29,34; 29,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,33; 29,96</t>
+          <t>29,28; 29,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 31,54</t>
+          <t>30,01; 30,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,37; 29,87</t>
+          <t>29,36; 29,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 30,14</t>
+          <t>29,69; 30,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,95</t>
+          <t>29,51; 29,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,48; 31,25</t>
+          <t>30,21; 30,66</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,94</t>
+          <t>30,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,44</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,69</t>
+          <t>30,33</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 30,25</t>
+          <t>29,88; 30,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,41; 30,76</t>
+          <t>30,41; 30,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,83</t>
+          <t>29,49; 29,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,57; 31,86</t>
+          <t>30,27; 30,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,16; 29,53</t>
+          <t>29,14; 29,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 30,2</t>
+          <t>29,85; 30,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 29,61</t>
+          <t>29,28; 29,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,24; 30,75</t>
+          <t>30,02; 30,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,56; 29,83</t>
+          <t>29,55; 29,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,68</t>
+          <t>29,44; 29,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,47; 31,21</t>
+          <t>30,2; 30,45</t>
         </is>
       </c>
     </row>
